--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_all_temperatures.xlsx
@@ -509,13 +509,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>26.2</v>
+        <v>31.7</v>
       </c>
       <c r="E3" t="n">
-        <v>17.4</v>
+        <v>16.9</v>
       </c>
       <c r="F3" t="n">
-        <v>21.8</v>
+        <v>24.3</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -532,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>32.2</v>
+        <v>26.2</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>17.4</v>
       </c>
       <c r="F4" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -554,15 +554,9 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F5" t="n">
-        <v>25.2</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -578,13 +572,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>26.8</v>
+        <v>30.5</v>
       </c>
       <c r="E6" t="n">
-        <v>18.4</v>
+        <v>19.9</v>
       </c>
       <c r="F6" t="n">
-        <v>22.6</v>
+        <v>25.2</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -600,15 +594,9 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -640,15 +628,9 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -663,15 +645,9 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>22.6</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -686,9 +662,15 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>22.6</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -738,13 +720,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>30.6</v>
+        <v>30.9</v>
       </c>
       <c r="E14" t="n">
-        <v>17.6</v>
+        <v>13.8</v>
       </c>
       <c r="F14" t="n">
-        <v>24.1</v>
+        <v>22.4</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -760,15 +742,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E15" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -783,9 +759,15 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23.5</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -800,15 +782,9 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -823,15 +799,9 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E18" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -846,15 +816,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -869,15 +833,9 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E20" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F20" t="n">
-        <v>24.3</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -893,13 +851,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>30.2</v>
+        <v>32.7</v>
       </c>
       <c r="E21" t="n">
-        <v>18.5</v>
+        <v>15.9</v>
       </c>
       <c r="F21" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -932,15 +890,9 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E23" t="n">
-        <v>18</v>
-      </c>
-      <c r="F23" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -955,15 +907,9 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>25.8</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1029,9 +975,15 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>25.6</v>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1047,10 +999,10 @@
         <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>31.8</v>
+        <v>32.5</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="F29" t="n">
         <v>25.4</v>
@@ -1070,13 +1022,13 @@
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>32.4</v>
+        <v>32.8</v>
       </c>
       <c r="E30" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="F30" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_all_temperatures.xlsx
@@ -486,13 +486,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="E2" t="n">
         <v>16.9</v>
       </c>
       <c r="F2" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -509,13 +509,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>31.7</v>
+        <v>26.2</v>
       </c>
       <c r="E3" t="n">
-        <v>16.9</v>
+        <v>11.4</v>
       </c>
       <c r="F3" t="n">
-        <v>24.3</v>
+        <v>18.8</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -532,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>26.2</v>
+        <v>32.4</v>
       </c>
       <c r="E4" t="n">
-        <v>17.4</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>21.8</v>
+        <v>27.7</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -554,9 +554,15 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>25.2</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -572,13 +578,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>30.5</v>
+        <v>26.8</v>
       </c>
       <c r="E6" t="n">
-        <v>19.9</v>
+        <v>18.4</v>
       </c>
       <c r="F6" t="n">
-        <v>25.2</v>
+        <v>22.6</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -594,9 +600,15 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>29</v>
+      </c>
+      <c r="E7" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23.9</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -611,9 +623,15 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>22.4</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -628,9 +646,15 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22.7</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -645,9 +669,15 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -663,13 +693,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="E11" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F11" t="n">
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -702,9 +732,15 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -719,15 +755,9 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E14" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -742,9 +772,15 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23.4</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -760,10 +796,10 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>38.5</v>
+        <v>29.2</v>
       </c>
       <c r="E16" t="n">
-        <v>8.5</v>
+        <v>17.8</v>
       </c>
       <c r="F16" t="n">
         <v>23.5</v>
@@ -782,9 +818,15 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24.2</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -799,9 +841,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>23.9</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -816,9 +864,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22.4</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -835,7 +889,9 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>24.3</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -851,13 +907,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>32.7</v>
+        <v>30.2</v>
       </c>
       <c r="E21" t="n">
-        <v>15.9</v>
+        <v>18.5</v>
       </c>
       <c r="F21" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -873,7 +929,9 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>32.8</v>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -890,9 +948,15 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>18</v>
+      </c>
+      <c r="F23" t="n">
+        <v>25.3</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -924,9 +988,15 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>27.4</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -941,9 +1011,15 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>19</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21.3</v>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -975,15 +1051,9 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E28" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F28" t="n">
-        <v>25.6</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -999,13 +1069,13 @@
         <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="E29" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="F29" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1021,15 +1091,9 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E30" t="n">
-        <v>19</v>
-      </c>
-      <c r="F30" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_all_temperatures.xlsx
@@ -486,13 +486,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>31.5</v>
+        <v>26.8</v>
       </c>
       <c r="E2" t="n">
-        <v>16.9</v>
+        <v>14.8</v>
       </c>
       <c r="F2" t="n">
-        <v>24.2</v>
+        <v>20.8</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -509,13 +509,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="E3" t="n">
-        <v>11.4</v>
+        <v>17.4</v>
       </c>
       <c r="F3" t="n">
-        <v>18.8</v>
+        <v>21.3</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -532,13 +532,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>32.4</v>
+        <v>38.2</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -604,10 +604,10 @@
         <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="F7" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -646,15 +646,9 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -669,15 +663,9 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="E10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -692,15 +680,9 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="E11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F11" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -755,9 +737,15 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23.7</v>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -772,15 +760,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -795,15 +777,9 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -819,14 +795,10 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24.2</v>
-      </c>
+        <v>28.8</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -842,10 +814,10 @@
         <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>29.6</v>
+        <v>28.6</v>
       </c>
       <c r="E18" t="n">
-        <v>18.2</v>
+        <v>19.2</v>
       </c>
       <c r="F18" t="n">
         <v>23.9</v>
@@ -887,8 +859,12 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>14.9</v>
+      </c>
       <c r="F20" t="n">
         <v>24.3</v>
       </c>
@@ -907,10 +883,10 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="E21" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="F21" t="n">
         <v>24.2</v>
@@ -929,9 +905,7 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="n">
-        <v>32.8</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
@@ -952,10 +926,10 @@
         <v>32.6</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="F23" t="n">
-        <v>25.3</v>
+        <v>25.8</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -971,9 +945,15 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>25.8</v>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -988,15 +968,9 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E25" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="F25" t="n">
-        <v>27.4</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1012,13 +986,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>23.6</v>
+        <v>33.6</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F26" t="n">
-        <v>21.3</v>
+        <v>25.8</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1051,9 +1025,15 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>25.4</v>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1069,13 +1049,13 @@
         <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="E29" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1091,9 +1071,15 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E30" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>25.6</v>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_all_temperatures.xlsx
@@ -486,13 +486,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>26.8</v>
+        <v>31.7</v>
       </c>
       <c r="E2" t="n">
-        <v>14.8</v>
+        <v>16.9</v>
       </c>
       <c r="F2" t="n">
-        <v>20.8</v>
+        <v>24.3</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -508,15 +508,9 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -531,15 +525,9 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>17</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -648,7 +636,9 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>22.7</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -663,9 +653,15 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -680,9 +676,15 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>23.4</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -718,7 +720,7 @@
         <v>30.6</v>
       </c>
       <c r="E13" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="F13" t="n">
         <v>24.1</v>
@@ -737,15 +739,9 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -794,11 +790,11 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="n">
-        <v>28.8</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>24.2</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -837,7 +833,7 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="E19" t="n">
         <v>17.5</v>
@@ -860,10 +856,10 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>33.7</v>
+        <v>32.7</v>
       </c>
       <c r="E20" t="n">
-        <v>14.9</v>
+        <v>15.9</v>
       </c>
       <c r="F20" t="n">
         <v>24.3</v>
@@ -922,15 +918,9 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E23" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F23" t="n">
-        <v>25.8</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -946,7 +936,7 @@
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="E24" t="n">
         <v>19.5</v>
@@ -985,15 +975,9 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E26" t="n">
-        <v>18</v>
-      </c>
-      <c r="F26" t="n">
-        <v>25.8</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1048,15 +1032,9 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>19</v>
-      </c>
-      <c r="F29" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1071,15 +1049,9 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E30" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F30" t="n">
-        <v>25.6</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
